--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_TOBARRA CB.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_TOBARRA CB.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. NVE MALEVA</t>
+          <t>R. KOWALSKI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>28.8964</v>
+        <v>24.0433</v>
       </c>
       <c r="E2" t="n">
-        <v>39.9114</v>
+        <v>33.2461</v>
       </c>
       <c r="F2" t="n">
-        <v>-11.0145</v>
+        <v>-9.202999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>13.5293</v>
+        <v>6.6159</v>
       </c>
       <c r="H2" t="n">
-        <v>13.8401</v>
+        <v>-6.118999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3104000000000001</v>
+        <v>12.7352</v>
       </c>
       <c r="J2" t="n">
-        <v>26.9176</v>
+        <v>33.9321</v>
       </c>
       <c r="K2" t="n">
-        <v>23.0902</v>
+        <v>12.9269</v>
       </c>
       <c r="L2" t="n">
-        <v>3.8276</v>
+        <v>21.0055</v>
       </c>
       <c r="M2" t="n">
-        <v>-13.3879</v>
+        <v>-27.3164</v>
       </c>
       <c r="N2" t="n">
-        <v>-9.2502</v>
+        <v>-19.0458</v>
       </c>
       <c r="O2" t="n">
-        <v>-4.1381</v>
+        <v>-8.270399999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>3.2825</v>
+        <v>-5.599299999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>-20.8528</v>
+        <v>-31.858</v>
       </c>
       <c r="R2" t="n">
-        <v>24.1347</v>
+        <v>26.2587</v>
       </c>
       <c r="S2" t="n">
-        <v>35.9824</v>
+        <v>-0.0411999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>33.1728</v>
+        <v>0.8631</v>
       </c>
       <c r="U2" t="n">
-        <v>2.8096</v>
+        <v>-0.9044999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>-23.8974</v>
+        <v>23.0676</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6735000000000002</v>
+        <v>30.3085</v>
       </c>
       <c r="X2" t="n">
-        <v>-24.5712</v>
+        <v>-7.2409</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. KOWALSKI</t>
+          <t>C. TEASLEY JR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>19.2742</v>
+        <v>13.4815</v>
       </c>
       <c r="E3" t="n">
-        <v>30.447</v>
+        <v>17.9483</v>
       </c>
       <c r="F3" t="n">
-        <v>-11.1726</v>
+        <v>-4.466900000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>6.6159</v>
+        <v>16.4078</v>
       </c>
       <c r="H3" t="n">
-        <v>-6.118999999999999</v>
+        <v>-1.8269</v>
       </c>
       <c r="I3" t="n">
-        <v>12.7352</v>
+        <v>18.2348</v>
       </c>
       <c r="J3" t="n">
-        <v>33.9321</v>
+        <v>30.6278</v>
       </c>
       <c r="K3" t="n">
-        <v>12.9269</v>
+        <v>5.9044</v>
       </c>
       <c r="L3" t="n">
-        <v>21.0055</v>
+        <v>24.7234</v>
       </c>
       <c r="M3" t="n">
-        <v>-27.3164</v>
+        <v>-14.22</v>
       </c>
       <c r="N3" t="n">
-        <v>-19.0458</v>
+        <v>-7.731199999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-8.270399999999999</v>
+        <v>-6.489</v>
       </c>
       <c r="P3" t="n">
-        <v>-5.599299999999999</v>
+        <v>-1.7377</v>
       </c>
       <c r="Q3" t="n">
-        <v>-31.858</v>
+        <v>-18.3426</v>
       </c>
       <c r="R3" t="n">
-        <v>26.2587</v>
+        <v>16.6047</v>
       </c>
       <c r="S3" t="n">
-        <v>-4.81</v>
+        <v>0.49</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.9361</v>
+        <v>1.4511</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.874</v>
+        <v>-0.9612000000000002</v>
       </c>
       <c r="V3" t="n">
-        <v>23.0676</v>
+        <v>-1.6788</v>
       </c>
       <c r="W3" t="n">
-        <v>30.3085</v>
+        <v>4.211600000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>-7.2409</v>
+        <v>-5.890400000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. TEASLEY JR</t>
+          <t>L. NVE MALEVA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>9.307200000000002</v>
+        <v>5.9193</v>
       </c>
       <c r="E4" t="n">
-        <v>14.9489</v>
+        <v>19.2547</v>
       </c>
       <c r="F4" t="n">
-        <v>-5.6421</v>
+        <v>-13.3356</v>
       </c>
       <c r="G4" t="n">
-        <v>16.4078</v>
+        <v>13.5293</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.8269</v>
+        <v>13.8401</v>
       </c>
       <c r="I4" t="n">
-        <v>18.2348</v>
+        <v>-0.3104000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>30.6278</v>
+        <v>26.9176</v>
       </c>
       <c r="K4" t="n">
-        <v>5.9044</v>
+        <v>23.0902</v>
       </c>
       <c r="L4" t="n">
-        <v>24.7234</v>
+        <v>3.8276</v>
       </c>
       <c r="M4" t="n">
-        <v>-14.22</v>
+        <v>-13.3879</v>
       </c>
       <c r="N4" t="n">
-        <v>-7.731199999999999</v>
+        <v>-9.2502</v>
       </c>
       <c r="O4" t="n">
-        <v>-6.489</v>
+        <v>-4.1381</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.7377</v>
+        <v>3.2825</v>
       </c>
       <c r="Q4" t="n">
-        <v>-18.3426</v>
+        <v>-20.8528</v>
       </c>
       <c r="R4" t="n">
-        <v>16.6047</v>
+        <v>24.1347</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.6842</v>
+        <v>13.0045</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.5482</v>
+        <v>12.5161</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.1361</v>
+        <v>0.4886000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.6788</v>
+        <v>-23.8974</v>
       </c>
       <c r="W4" t="n">
-        <v>4.211600000000001</v>
+        <v>0.6735000000000002</v>
       </c>
       <c r="X4" t="n">
-        <v>-5.890400000000001</v>
+        <v>-24.5712</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Á. GONZÁLEZ CLEMENTE</t>
+          <t>A. PUJADAS TARRADELLAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.09389999999999998</v>
+        <v>2.136599999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0345</v>
+        <v>20.3828</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.05940000000000001</v>
+        <v>-18.2464</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1104</v>
+        <v>-31.6638</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0207</v>
+        <v>-13.9435</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1311</v>
+        <v>-17.7202</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0207</v>
+        <v>19.9149</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0207</v>
+        <v>18.3563</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.558300000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1311</v>
+        <v>-51.5785</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-32.2998</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1311</v>
+        <v>-19.2786</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-4.054499999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-57.3443</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>53.2896</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0166</v>
+        <v>-9.288600000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0552</v>
+        <v>-2.8605</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0717</v>
+        <v>-6.4279</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>47.1434</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>60.6728</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-13.5294</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. ALFARO OCHOA</t>
+          <t>Á. GONZÁLEZ CLEMENTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,43 +874,43 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4739</v>
+        <v>0.03440000000000004</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0145</v>
+        <v>0.0689</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4594</v>
+        <v>-0.03449999999999998</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4353</v>
+        <v>-0.1104</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.0207</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3662</v>
+        <v>-0.1311</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0407</v>
+        <v>0.0207</v>
       </c>
       <c r="K6" t="n">
+        <v>0.0207</v>
+      </c>
+      <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
-        <v>0.0407</v>
-      </c>
       <c r="M6" t="n">
-        <v>-0.4759</v>
+        <v>-0.1311</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4069</v>
+        <v>-0.1311</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0386</v>
+        <v>0.1448</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0552</v>
+        <v>0.0482</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0166</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. KARAMPELAS</t>
+          <t>D. ALFARO OCHOA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-6.3516</v>
+        <v>-0.4491</v>
       </c>
       <c r="E7" t="n">
-        <v>-6.9643</v>
+        <v>-0.0145</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6127</v>
+        <v>-0.4346</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.2066</v>
+        <v>-0.4353</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0131</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-5.2197</v>
+        <v>-0.3662</v>
       </c>
       <c r="J7" t="n">
-        <v>-4.5367</v>
+        <v>0.0407</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2897</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.8264</v>
+        <v>0.0407</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.67</v>
+        <v>-0.4759</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2766</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3934</v>
+        <v>-0.4069</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1239</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9308</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3807</v>
+        <v>-0.0138</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3038</v>
+        <v>-0.0552</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0769</v>
+        <v>0.0414</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. DEUS VERA</t>
+          <t>S. KONTE SYLLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>-7.6882</v>
+        <v>-4.4591</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.668599999999999</v>
+        <v>-2.966000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.0197</v>
+        <v>-1.4929</v>
       </c>
       <c r="G8" t="n">
-        <v>-6.4556</v>
+        <v>-3.166</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.9918</v>
+        <v>4.5317</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4634999999999998</v>
+        <v>-7.6978</v>
       </c>
       <c r="J8" t="n">
-        <v>2.7449</v>
+        <v>12.6746</v>
       </c>
       <c r="K8" t="n">
-        <v>2.5639</v>
+        <v>15.5043</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1811</v>
+        <v>-2.8298</v>
       </c>
       <c r="M8" t="n">
-        <v>-9.2003</v>
+        <v>-15.8406</v>
       </c>
       <c r="N8" t="n">
-        <v>-8.5556</v>
+        <v>-10.9726</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6445999999999998</v>
+        <v>-4.8678</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.4755</v>
+        <v>-7.143899999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-13.7087</v>
+        <v>-23.9418</v>
       </c>
       <c r="R8" t="n">
-        <v>10.2331</v>
+        <v>16.7977</v>
       </c>
       <c r="S8" t="n">
-        <v>5.3118</v>
+        <v>-0.4828999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>6.3963</v>
+        <v>-0.2802</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0846</v>
+        <v>-0.2025999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.0693</v>
+        <v>6.3339</v>
       </c>
       <c r="W8" t="n">
-        <v>2.8987</v>
+        <v>8.581300000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>-5.9679</v>
+        <v>-2.2473</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. KONTE SYLLA</t>
+          <t>A. KARAMPELAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.7161</v>
+        <v>-6.0951</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.668899999999999</v>
+        <v>-6.7575</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.047</v>
+        <v>0.6624</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.166</v>
+        <v>-5.2066</v>
       </c>
       <c r="H9" t="n">
-        <v>4.5317</v>
+        <v>0.0131</v>
       </c>
       <c r="I9" t="n">
-        <v>-7.6978</v>
+        <v>-5.2197</v>
       </c>
       <c r="J9" t="n">
-        <v>12.6746</v>
+        <v>-4.5367</v>
       </c>
       <c r="K9" t="n">
-        <v>15.5043</v>
+        <v>0.2897</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.8298</v>
+        <v>-4.8264</v>
       </c>
       <c r="M9" t="n">
-        <v>-15.8406</v>
+        <v>-0.67</v>
       </c>
       <c r="N9" t="n">
-        <v>-10.9726</v>
+        <v>-0.2766</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.8678</v>
+        <v>-0.3934</v>
       </c>
       <c r="P9" t="n">
-        <v>-7.143899999999999</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q9" t="n">
-        <v>-23.9418</v>
+        <v>-2.1239</v>
       </c>
       <c r="R9" t="n">
-        <v>16.7977</v>
+        <v>1.9308</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.74</v>
+        <v>-0.1242</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.983</v>
+        <v>-0.097</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7569</v>
+        <v>-0.0272</v>
       </c>
       <c r="V9" t="n">
-        <v>6.3339</v>
+        <v>-0.5712</v>
       </c>
       <c r="W9" t="n">
-        <v>8.581300000000001</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.2473</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.8379</v>
+        <v>-7.2698</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.632800000000001</v>
+        <v>-1.4261</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.2051</v>
+        <v>-5.8437</v>
       </c>
       <c r="G10" t="n">
         <v>-7.41</v>
@@ -1234,13 +1234,13 @@
         <v>7.9162</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3129</v>
+        <v>-0.7445999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1327</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1803000000000001</v>
+        <v>0.1811</v>
       </c>
       <c r="V10" t="n">
         <v>-2.7835</v>
@@ -1267,13 +1267,13 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.9676</v>
+        <v>-8.369</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.2886</v>
+        <v>-5.391999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.679</v>
+        <v>-2.9769</v>
       </c>
       <c r="G11" t="n">
         <v>-4.9428</v>
@@ -1312,13 +1312,13 @@
         <v>2.1239</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3915</v>
+        <v>-0.7929</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6626000000000001</v>
+        <v>-0.766</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2711</v>
+        <v>-0.02689999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-2.8263</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Y. BOUBACAR</t>
+          <t>R. DEUS VERA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.1111</v>
+        <v>-10.2902</v>
       </c>
       <c r="E12" t="n">
-        <v>17.6183</v>
+        <v>-4.5574</v>
       </c>
       <c r="F12" t="n">
-        <v>-25.7296</v>
+        <v>-5.7328</v>
       </c>
       <c r="G12" t="n">
-        <v>-15.7449</v>
+        <v>-6.4556</v>
       </c>
       <c r="H12" t="n">
-        <v>-7.9537</v>
+        <v>-5.9918</v>
       </c>
       <c r="I12" t="n">
-        <v>-7.7915</v>
+        <v>-0.4634999999999998</v>
       </c>
       <c r="J12" t="n">
-        <v>26.6488</v>
+        <v>2.7449</v>
       </c>
       <c r="K12" t="n">
-        <v>20.3393</v>
+        <v>2.5639</v>
       </c>
       <c r="L12" t="n">
-        <v>6.3099</v>
+        <v>0.1811</v>
       </c>
       <c r="M12" t="n">
-        <v>-42.3938</v>
+        <v>-9.2003</v>
       </c>
       <c r="N12" t="n">
-        <v>-28.2924</v>
+        <v>-8.5556</v>
       </c>
       <c r="O12" t="n">
-        <v>-14.1012</v>
+        <v>-0.6445999999999998</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.544900000000001</v>
+        <v>-3.4755</v>
       </c>
       <c r="Q12" t="n">
-        <v>-37.6505</v>
+        <v>-13.7087</v>
       </c>
       <c r="R12" t="n">
-        <v>36.1052</v>
+        <v>10.2331</v>
       </c>
       <c r="S12" t="n">
-        <v>19.3954</v>
+        <v>2.7099</v>
       </c>
       <c r="T12" t="n">
-        <v>16.8971</v>
+        <v>3.5074</v>
       </c>
       <c r="U12" t="n">
-        <v>2.4983</v>
+        <v>-0.7975999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-10.2171</v>
+        <v>-3.0693</v>
       </c>
       <c r="W12" t="n">
-        <v>11.7229</v>
+        <v>2.8987</v>
       </c>
       <c r="X12" t="n">
-        <v>-21.9397</v>
+        <v>-5.9679</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. KALINICENKO</t>
+          <t>E. RAMÓN FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.7277</v>
+        <v>-12.0502</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.306100000000001</v>
+        <v>-6.349</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4216</v>
+        <v>-5.7009</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.7971</v>
+        <v>-8.8306</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.5606</v>
+        <v>-5.1864</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.2366</v>
+        <v>-3.6445</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6330000000000002</v>
+        <v>19.0855</v>
       </c>
       <c r="K13" t="n">
-        <v>2.2355</v>
+        <v>15.1058</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.8686</v>
+        <v>3.9797</v>
       </c>
       <c r="M13" t="n">
-        <v>-7.1642</v>
+        <v>-27.9158</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.7962</v>
+        <v>-20.2919</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3681</v>
+        <v>-7.6243</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.1238</v>
+        <v>5.4061</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.0747</v>
+        <v>-32.8235</v>
       </c>
       <c r="R13" t="n">
-        <v>6.950799999999999</v>
+        <v>38.2294</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3204</v>
+        <v>-5.4413</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4978999999999998</v>
+        <v>-0.6636</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8183</v>
+        <v>-4.7778</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.1271</v>
+        <v>-3.184400000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>0.8995</v>
+        <v>8.0524</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.0266</v>
+        <v>-11.2367</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. PUJADAS TARRADELLAS</t>
+          <t>A. KALINICENKO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.2164</v>
+        <v>-12.0619</v>
       </c>
       <c r="E14" t="n">
-        <v>8.502900000000002</v>
+        <v>-9.306100000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-21.7192</v>
+        <v>-2.7557</v>
       </c>
       <c r="G14" t="n">
-        <v>-31.6638</v>
+        <v>-7.7971</v>
       </c>
       <c r="H14" t="n">
-        <v>-13.9435</v>
+        <v>-3.5606</v>
       </c>
       <c r="I14" t="n">
-        <v>-17.7202</v>
+        <v>-4.2366</v>
       </c>
       <c r="J14" t="n">
-        <v>19.9149</v>
+        <v>-0.6330000000000002</v>
       </c>
       <c r="K14" t="n">
-        <v>18.3563</v>
+        <v>2.2355</v>
       </c>
       <c r="L14" t="n">
-        <v>1.558300000000001</v>
+        <v>-2.8686</v>
       </c>
       <c r="M14" t="n">
-        <v>-51.5785</v>
+        <v>-7.1642</v>
       </c>
       <c r="N14" t="n">
-        <v>-32.2998</v>
+        <v>-5.7962</v>
       </c>
       <c r="O14" t="n">
-        <v>-19.2786</v>
+        <v>-1.3681</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.054499999999999</v>
+        <v>-2.1238</v>
       </c>
       <c r="Q14" t="n">
-        <v>-57.3443</v>
+        <v>-9.0747</v>
       </c>
       <c r="R14" t="n">
-        <v>53.2896</v>
+        <v>6.950799999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-24.641</v>
+        <v>-0.01359999999999995</v>
       </c>
       <c r="T14" t="n">
-        <v>-14.7403</v>
+        <v>-0.4978999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-9.900400000000001</v>
+        <v>0.4844000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>47.1434</v>
+        <v>-2.1271</v>
       </c>
       <c r="W14" t="n">
-        <v>60.6728</v>
+        <v>0.8995</v>
       </c>
       <c r="X14" t="n">
-        <v>-13.5294</v>
+        <v>-3.0266</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>-22.7942</v>
+        <v>-18.8799</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3752</v>
+        <v>3.3473</v>
       </c>
       <c r="F15" t="n">
-        <v>-24.1696</v>
+        <v>-22.2273</v>
       </c>
       <c r="G15" t="n">
         <v>-3.460399999999999</v>
@@ -1624,13 +1624,13 @@
         <v>15.0599</v>
       </c>
       <c r="S15" t="n">
-        <v>-6.8795</v>
+        <v>-2.9652</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.32</v>
+        <v>-0.3482</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.5592</v>
+        <v>-2.617</v>
       </c>
       <c r="V15" t="n">
         <v>-6.4693</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. RAMÓN FERNÁNDEZ</t>
+          <t>Y. BOUBACAR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>25</v>
       </c>
       <c r="D16" t="n">
-        <v>-25.1783</v>
+        <v>-23.3348</v>
       </c>
       <c r="E16" t="n">
-        <v>-14.547</v>
+        <v>4.704600000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-10.631</v>
+        <v>-28.0396</v>
       </c>
       <c r="G16" t="n">
-        <v>-8.8306</v>
+        <v>-15.7449</v>
       </c>
       <c r="H16" t="n">
-        <v>-5.1864</v>
+        <v>-7.9537</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.6445</v>
+        <v>-7.7915</v>
       </c>
       <c r="J16" t="n">
-        <v>19.0855</v>
+        <v>26.6488</v>
       </c>
       <c r="K16" t="n">
-        <v>15.1058</v>
+        <v>20.3393</v>
       </c>
       <c r="L16" t="n">
-        <v>3.9797</v>
+        <v>6.3099</v>
       </c>
       <c r="M16" t="n">
-        <v>-27.9158</v>
+        <v>-42.3938</v>
       </c>
       <c r="N16" t="n">
-        <v>-20.2919</v>
+        <v>-28.2924</v>
       </c>
       <c r="O16" t="n">
-        <v>-7.6243</v>
+        <v>-14.1012</v>
       </c>
       <c r="P16" t="n">
-        <v>5.4061</v>
+        <v>-1.544900000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>-32.8235</v>
+        <v>-37.6505</v>
       </c>
       <c r="R16" t="n">
-        <v>38.2294</v>
+        <v>36.1052</v>
       </c>
       <c r="S16" t="n">
-        <v>-18.5692</v>
+        <v>4.1716</v>
       </c>
       <c r="T16" t="n">
-        <v>-8.861700000000001</v>
+        <v>3.9832</v>
       </c>
       <c r="U16" t="n">
-        <v>-9.707599999999999</v>
+        <v>0.1883000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.184400000000001</v>
+        <v>-10.2171</v>
       </c>
       <c r="W16" t="n">
-        <v>8.0524</v>
+        <v>11.7229</v>
       </c>
       <c r="X16" t="n">
-        <v>-11.2367</v>
+        <v>-21.9397</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>-26.0481</v>
+        <v>-24.2897</v>
       </c>
       <c r="E17" t="n">
-        <v>-20.0306</v>
+        <v>-19.1962</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.0176</v>
+        <v>-5.0935</v>
       </c>
       <c r="G17" t="n">
         <v>-16.5556</v>
@@ -1780,13 +1780,13 @@
         <v>8.688499999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>-4.4411</v>
+        <v>-2.6826</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2988</v>
+        <v>-0.4645000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-3.1421</v>
+        <v>-2.2183</v>
       </c>
       <c r="V17" t="n">
         <v>-4.6652</v>
@@ -1813,13 +1813,13 @@
         <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>-27.0635</v>
+        <v>-26.9907</v>
       </c>
       <c r="E18" t="n">
-        <v>-21.5405</v>
+        <v>-21.3539</v>
       </c>
       <c r="F18" t="n">
-        <v>-5.523</v>
+        <v>-5.6366</v>
       </c>
       <c r="G18" t="n">
         <v>-23.9888</v>
@@ -1858,13 +1858,13 @@
         <v>21.4315</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.7759</v>
+        <v>-1.703</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5298000000000003</v>
+        <v>-0.3432999999999998</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.2462</v>
+        <v>-1.3596</v>
       </c>
       <c r="V18" t="n">
         <v>5.8452</v>
@@ -1891,13 +1891,13 @@
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>-31.6031</v>
+        <v>-30.4917</v>
       </c>
       <c r="E19" t="n">
-        <v>-6.757</v>
+        <v>-6.343400000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-24.846</v>
+        <v>-24.1481</v>
       </c>
       <c r="G19" t="n">
         <v>-22.0168</v>
@@ -1936,13 +1936,13 @@
         <v>13.5158</v>
       </c>
       <c r="S19" t="n">
-        <v>-6.3658</v>
+        <v>-5.2544</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3279</v>
+        <v>-0.9144000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-5.0378</v>
+        <v>-4.34</v>
       </c>
       <c r="V19" t="n">
         <v>-8.0474</v>
@@ -1969,13 +1969,13 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-62.6277</v>
+        <v>-53.1939</v>
       </c>
       <c r="E20" t="n">
-        <v>-39.0719</v>
+        <v>-31.7011</v>
       </c>
       <c r="F20" t="n">
-        <v>-23.5557</v>
+        <v>-21.4924</v>
       </c>
       <c r="G20" t="n">
         <v>-38.088</v>
@@ -2014,13 +2014,13 @@
         <v>39.5811</v>
       </c>
       <c r="S20" t="n">
-        <v>-12.544</v>
+        <v>-3.11</v>
       </c>
       <c r="T20" t="n">
-        <v>-6.849299999999999</v>
+        <v>0.5216</v>
       </c>
       <c r="U20" t="n">
-        <v>-5.6943</v>
+        <v>-3.6313</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2180999999999997</v>
@@ -2047,13 +2047,13 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>-209.0215</v>
+        <v>-192.61</v>
       </c>
       <c r="E21" t="n">
-        <v>-19.72159999999999</v>
+        <v>-16.41050000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-189.2994</v>
+        <v>-176.199</v>
       </c>
       <c r="G21" t="n">
         <v>-159.3197</v>
@@ -2083,7 +2083,7 @@
         <v>-99.1101</v>
       </c>
       <c r="P21" t="n">
-        <v>-33.7887</v>
+        <v>-33.78869999999999</v>
       </c>
       <c r="Q21" t="n">
         <v>-372.6433</v>
@@ -2092,13 +2092,13 @@
         <v>338.8516</v>
       </c>
       <c r="S21" t="n">
-        <v>-28.54780000000001</v>
+        <v>-12.1375</v>
       </c>
       <c r="T21" t="n">
-        <v>11.3637</v>
+        <v>14.674</v>
       </c>
       <c r="U21" t="n">
-        <v>-39.91079999999999</v>
+        <v>-26.8115</v>
       </c>
       <c r="V21" t="n">
         <v>12.63499999999999</v>
